--- a/STAM.xlsx
+++ b/STAM.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zaifu\Desktop\Telegram Kehadiran\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5ED7D5-5AC9-4FA3-8BD6-0249276BD9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293DF7C5-7C2D-4AB9-B9C1-F24332259914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LULU" sheetId="1" r:id="rId1"/>
-    <sheet name="MARJAN" sheetId="2" r:id="rId2"/>
+    <sheet name="STAMLULU" sheetId="1" r:id="rId1"/>
+    <sheet name="STAMMARJAN" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>ADLIN YUSRINA BINTI MOHD YUSOFF</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>SITI NUR SYAFIQAH BINTI MOHD RAHIMI</t>
+  </si>
+  <si>
+    <t>NUR DAMIA BATRISYA BINTI AHMAD DAUD</t>
   </si>
 </sst>
 </file>
@@ -217,13 +220,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.109375" style="2" customWidth="1"/>
@@ -516,36 +519,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -665,7 +668,7 @@
     </row>
     <row r="19" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="3"/>
@@ -674,7 +677,7 @@
     </row>
     <row r="20" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="3"/>
@@ -682,7 +685,9 @@
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="B21" s="7"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -702,9 +707,16 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
+    <row r="24" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:A23">
-    <sortCondition ref="A8:A23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:A24">
+    <sortCondition ref="A8:A24"/>
   </sortState>
   <mergeCells count="6">
     <mergeCell ref="B6:E6"/>
@@ -730,25 +742,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -758,15 +770,15 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
